--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_ANADOLU EFES ISTANBUL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_ANADOLU EFES ISTANBUL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA54"/>
+  <dimension ref="A1:BA52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,16 +671,16 @@
         <v>0.2292829540575354</v>
       </c>
       <c r="J2" t="n">
-        <v>310</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
-        <v>381</v>
+        <v>9</v>
       </c>
       <c r="L2" t="n">
-        <v>229</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="N2" t="n">
         <v>991</v>
@@ -752,13 +752,13 @@
         <v>1.065306122448979</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.6567796610169492</v>
+        <v>0.02542372881355932</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.067226890756303</v>
+        <v>0.02521008403361345</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.557823129251701</v>
+        <v>2.25</v>
       </c>
       <c r="AN2" t="n">
         <v>1.394957983193277</v>
@@ -801,16 +801,16 @@
         <v>0.2292829540575354</v>
       </c>
       <c r="J3" t="n">
-        <v>8.157894736842104</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="K3" t="n">
-        <v>10.02631578947368</v>
+        <v>0.2368421052631579</v>
       </c>
       <c r="L3" t="n">
-        <v>6.026315789473684</v>
+        <v>0.2368421052631579</v>
       </c>
       <c r="M3" t="n">
-        <v>10.8421052631579</v>
+        <v>10.81578947368421</v>
       </c>
       <c r="N3" t="n">
         <v>26.07894736842105</v>
@@ -882,13 +882,13 @@
         <v>1.06530612244898</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.6567796610169491</v>
+        <v>0.02542372881355932</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.067226890756303</v>
+        <v>0.02521008403361344</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.557823129251701</v>
+        <v>2.25</v>
       </c>
       <c r="AN3" t="n">
         <v>1.394957983193277</v>
@@ -931,16 +931,16 @@
         <v>0.271948608137045</v>
       </c>
       <c r="J4" t="n">
-        <v>328</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>431</v>
+        <v>16</v>
       </c>
       <c r="L4" t="n">
-        <v>314</v>
+        <v>18</v>
       </c>
       <c r="M4" t="n">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="N4" t="n">
         <v>1073</v>
@@ -1012,13 +1012,13 @@
         <v>1.093717816683831</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.6890756302521008</v>
+        <v>0.02100840336134454</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.061576354679803</v>
+        <v>0.03940886699507389</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.593908629441624</v>
+        <v>1.636363636363636</v>
       </c>
       <c r="AN4" t="n">
         <v>1.580508474576271</v>
@@ -1061,16 +1061,16 @@
         <v>0.271948608137045</v>
       </c>
       <c r="J5" t="n">
-        <v>8.631578947368421</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="K5" t="n">
-        <v>11.3421052631579</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="L5" t="n">
-        <v>8.263157894736842</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="M5" t="n">
-        <v>11.23684210526316</v>
+        <v>11.21052631578947</v>
       </c>
       <c r="N5" t="n">
         <v>28.23684210526316</v>
@@ -1142,13 +1142,13 @@
         <v>1.093717816683831</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.6890756302521008</v>
+        <v>0.02100840336134454</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.061576354679803</v>
+        <v>0.03940886699507389</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.593908629441624</v>
+        <v>1.636363636363636</v>
       </c>
       <c r="AN5" t="n">
         <v>1.580508474576271</v>
@@ -1486,16 +1486,16 @@
         <v>201</v>
       </c>
       <c r="U8" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="V8" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="W8" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>46</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>663:31</t>
+          <t>358:15</t>
         </is>
       </c>
       <c r="AO8" t="n">
@@ -1575,13 +1575,13 @@
         <v>6</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.131</v>
+        <v>0.243</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.011</v>
+        <v>0.02</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.041</v>
+        <v>0.076</v>
       </c>
       <c r="BA8" t="n">
         <v>0.049</v>
@@ -1651,16 +1651,16 @@
         <v>102</v>
       </c>
       <c r="U9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>13</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>628:02</t>
+          <t>255:31</t>
         </is>
       </c>
       <c r="AO9" t="n">
@@ -1740,13 +1740,13 @@
         <v>11.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.083</v>
+        <v>0.204</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.004</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.047</v>
+        <v>0.116</v>
       </c>
       <c r="BA9" t="n">
         <v>0.022</v>
@@ -1816,16 +1816,16 @@
         <v>154</v>
       </c>
       <c r="U10" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
         <v>68</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>866:30</t>
+          <t>435:03</t>
         </is>
       </c>
       <c r="AO10" t="n">
@@ -1905,13 +1905,13 @@
         <v>6.862</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.121</v>
+        <v>0.242</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.011</v>
+        <v>0.022</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.033</v>
+        <v>0.065</v>
       </c>
       <c r="BA10" t="n">
         <v>0.035</v>
@@ -1981,16 +1981,16 @@
         <v>395</v>
       </c>
       <c r="U11" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
         <v>131</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>1541:04</t>
+          <t>794:06</t>
         </is>
       </c>
       <c r="AO11" t="n">
@@ -2070,13 +2070,13 @@
         <v>8.452</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.123</v>
+        <v>0.239</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.017</v>
+        <v>0.032</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.051</v>
+        <v>0.1</v>
       </c>
       <c r="BA11" t="n">
         <v>0.065</v>
@@ -2146,16 +2146,16 @@
         <v>211</v>
       </c>
       <c r="U12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>83</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>678:05</t>
+          <t>327:40</t>
         </is>
       </c>
       <c r="AO12" t="n">
@@ -2235,13 +2235,13 @@
         <v>9.157999999999999</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.128</v>
+        <v>0.265</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.011</v>
+        <v>0.022</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.038</v>
+        <v>0.079</v>
       </c>
       <c r="BA12" t="n">
         <v>0.048</v>
@@ -2464,7 +2464,7 @@
         <v>59</v>
       </c>
       <c r="Q14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R14" t="n">
         <v>91</v>
@@ -2476,16 +2476,16 @@
         <v>423</v>
       </c>
       <c r="U14" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="V14" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="X14" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
         <v>74</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2063:45</t>
+          <t>1055:33</t>
         </is>
       </c>
       <c r="AO14" t="n">
@@ -2565,13 +2565,13 @@
         <v>6.831</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.075</v>
+        <v>0.146</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.016</v>
+        <v>0.032</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.058</v>
+        <v>0.114</v>
       </c>
       <c r="BA14" t="n">
         <v>0.18</v>
@@ -2644,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>134:08</t>
+          <t>73:53</t>
         </is>
       </c>
       <c r="AO15" t="n">
@@ -2730,13 +2730,13 @@
         <v>10</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.063</v>
+        <v>0.114</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.045</v>
+        <v>0.082</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.111</v>
+        <v>0.201</v>
       </c>
       <c r="BA15" t="n">
         <v>0.005</v>
@@ -2806,16 +2806,16 @@
         <v>287</v>
       </c>
       <c r="U16" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="V16" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>99</v>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>1470:11</t>
+          <t>721:07</t>
         </is>
       </c>
       <c r="AO16" t="n">
@@ -2895,13 +2895,13 @@
         <v>6.341</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.1</v>
+        <v>0.204</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.015</v>
+        <v>0.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.056</v>
+        <v>0.115</v>
       </c>
       <c r="BA16" t="n">
         <v>0.059</v>
@@ -2971,16 +2971,16 @@
         <v>233</v>
       </c>
       <c r="U17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="W17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>78</v>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>1313:12</t>
+          <t>658:06</t>
         </is>
       </c>
       <c r="AO17" t="n">
@@ -3060,13 +3060,13 @@
         <v>7.214</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.168</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.03</v>
+        <v>0.061</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.139</v>
       </c>
       <c r="BA17" t="n">
         <v>0.026</v>
@@ -3136,16 +3136,16 @@
         <v>111</v>
       </c>
       <c r="U18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>44</v>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>429:39</t>
+          <t>219:42</t>
         </is>
       </c>
       <c r="AO18" t="n">
@@ -3225,13 +3225,13 @@
         <v>4.4</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.094</v>
+        <v>0.184</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.065</v>
+        <v>0.127</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.058</v>
+        <v>0.113</v>
       </c>
       <c r="BA18" t="n">
         <v>0.006</v>
@@ -3301,16 +3301,16 @@
         <v>216</v>
       </c>
       <c r="U19" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>53</v>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>1141:53</t>
+          <t>566:32</t>
         </is>
       </c>
       <c r="AO19" t="n">
@@ -3390,13 +3390,13 @@
         <v>7.732</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.135</v>
+        <v>0.272</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.017</v>
+        <v>0.034</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.051</v>
+        <v>0.103</v>
       </c>
       <c r="BA19" t="n">
         <v>0.066</v>
@@ -3466,16 +3466,16 @@
         <v>163</v>
       </c>
       <c r="U20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
         <v>56</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>479:19</t>
+          <t>254:17</t>
         </is>
       </c>
       <c r="AO20" t="n">
@@ -3555,13 +3555,13 @@
         <v>10.1</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.111</v>
+        <v>0.21</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.073</v>
+        <v>0.138</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.093</v>
+        <v>0.175</v>
       </c>
       <c r="BA20" t="n">
         <v>0.016</v>
@@ -3796,16 +3796,16 @@
         <v>124</v>
       </c>
       <c r="U22" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
         <v>26</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>670:40</t>
+          <t>270:23</t>
         </is>
       </c>
       <c r="AO22" t="n">
@@ -3885,13 +3885,13 @@
         <v>15.714</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.215</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.022</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.05</v>
+        <v>0.123</v>
       </c>
       <c r="BA22" t="n">
         <v>0.008</v>
@@ -3964,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>99:46</t>
+          <t>49:46</t>
         </is>
       </c>
       <c r="AO23" t="n">
@@ -4050,13 +4050,13 @@
         <v>8</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.118</v>
+        <v>0.237</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.012</v>
+        <v>0.024</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.012</v>
+        <v>0.025</v>
       </c>
       <c r="BA23" t="n">
         <v>0.004</v>
@@ -4126,16 +4126,16 @@
         <v>444</v>
       </c>
       <c r="U24" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="X24" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
         <v>125</v>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>1627:07</t>
+          <t>874:39</t>
         </is>
       </c>
       <c r="AO24" t="n">
@@ -4215,13 +4215,13 @@
         <v>4.562</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.119</v>
+        <v>0.221</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.033</v>
+        <v>0.061</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.093</v>
+        <v>0.172</v>
       </c>
       <c r="BA24" t="n">
         <v>0.051</v>
@@ -4291,16 +4291,16 @@
         <v>42</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
         <v>17</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>410:10</t>
+          <t>203:49</t>
         </is>
       </c>
       <c r="AO25" t="n">
@@ -4380,13 +4380,13 @@
         <v>2.833</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.051</v>
+        <v>0.103</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.024</v>
+        <v>0.048</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="BA25" t="n">
         <v>0.011</v>
@@ -4456,16 +4456,16 @@
         <v>271</v>
       </c>
       <c r="U26" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="W26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>71</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>1198:43</t>
+          <t>556:32</t>
         </is>
       </c>
       <c r="AO26" t="n">
@@ -4545,13 +4545,13 @@
         <v>4.706</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.037</v>
+        <v>0.079</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.042</v>
+        <v>0.089</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.089</v>
+        <v>0.191</v>
       </c>
       <c r="BA26" t="n">
         <v>0.017</v>
@@ -4725,163 +4725,163 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>38</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>3044</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>733</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1349</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>534</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>681</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>664</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>836</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>476</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>411</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>712</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>758</v>
       </c>
       <c r="T28" t="n">
-        <v>93</v>
+        <v>3508</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>991</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>0.834</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>562</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>0.301</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>0.438</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>836</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>0.341</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>7675:00</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>35</v>
+        <v>3104.64</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>0.539</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>0.153</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>0.229</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>1.395</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>4.893</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>6.288</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="BA28" t="n">
         <v>0</v>
@@ -4890,44 +4890,44 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>38</v>
       </c>
       <c r="C29" t="n">
-        <v>3044</v>
+        <v>3205</v>
       </c>
       <c r="D29" t="n">
-        <v>733</v>
+        <v>754</v>
       </c>
       <c r="E29" t="n">
-        <v>1349</v>
+        <v>1364</v>
       </c>
       <c r="F29" t="n">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="G29" t="n">
-        <v>980</v>
+        <v>971</v>
       </c>
       <c r="H29" t="n">
-        <v>534</v>
+        <v>635</v>
       </c>
       <c r="I29" t="n">
-        <v>681</v>
+        <v>787</v>
       </c>
       <c r="J29" t="n">
-        <v>664</v>
+        <v>746</v>
       </c>
       <c r="K29" t="n">
-        <v>836</v>
+        <v>908</v>
       </c>
       <c r="L29" t="n">
-        <v>357</v>
+        <v>406</v>
       </c>
       <c r="M29" t="n">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="N29" t="n">
         <v>190</v>
@@ -4936,76 +4936,76 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="Q29" t="n">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="R29" t="n">
-        <v>712</v>
+        <v>685</v>
       </c>
       <c r="S29" t="n">
-        <v>758</v>
+        <v>790</v>
       </c>
       <c r="T29" t="n">
-        <v>3508</v>
+        <v>3927</v>
       </c>
       <c r="U29" t="n">
-        <v>310</v>
+        <v>10</v>
       </c>
       <c r="V29" t="n">
-        <v>381</v>
+        <v>16</v>
       </c>
       <c r="W29" t="n">
-        <v>229</v>
+        <v>18</v>
       </c>
       <c r="X29" t="n">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="Y29" t="n">
-        <v>991</v>
+        <v>1073</v>
       </c>
       <c r="Z29" t="n">
-        <v>1188</v>
+        <v>1261</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.834</v>
+        <v>0.851</v>
       </c>
       <c r="AB29" t="n">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="AC29" t="n">
-        <v>562</v>
+        <v>631</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.42</v>
+        <v>0.425</v>
       </c>
       <c r="AE29" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AF29" t="n">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.301</v>
+        <v>0.449</v>
       </c>
       <c r="AH29" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="AI29" t="n">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.438</v>
+        <v>0.505</v>
       </c>
       <c r="AK29" t="n">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="AL29" t="n">
-        <v>836</v>
+        <v>872</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.341</v>
+        <v>0.349</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
@@ -5013,40 +5013,40 @@
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>3104.64</v>
+        <v>3153.28</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.539</v>
+        <v>0.55</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.579</v>
+        <v>0.598</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.98</v>
+        <v>1.016</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.153</v>
+        <v>0.15</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.229</v>
+        <v>0.272</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.395</v>
+        <v>1.581</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.893</v>
+        <v>4.947</v>
       </c>
       <c r="AW29" t="n">
-        <v>6.288</v>
+        <v>6.528</v>
       </c>
       <c r="AX29" t="n">
         <v>0.2</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.056</v>
+        <v>0.065</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.135</v>
+        <v>0.144</v>
       </c>
       <c r="BA29" t="n">
         <v>0</v>
@@ -5055,2224 +5055,2224 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>38</v>
-      </c>
-      <c r="C30" t="n">
-        <v>3205</v>
-      </c>
-      <c r="D30" t="n">
-        <v>754</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1364</v>
-      </c>
-      <c r="F30" t="n">
-        <v>354</v>
-      </c>
-      <c r="G30" t="n">
-        <v>971</v>
-      </c>
-      <c r="H30" t="n">
-        <v>635</v>
-      </c>
-      <c r="I30" t="n">
-        <v>787</v>
-      </c>
-      <c r="J30" t="n">
-        <v>746</v>
-      </c>
-      <c r="K30" t="n">
-        <v>908</v>
-      </c>
-      <c r="L30" t="n">
-        <v>406</v>
-      </c>
-      <c r="M30" t="n">
-        <v>218</v>
-      </c>
-      <c r="N30" t="n">
-        <v>190</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>472</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>427</v>
-      </c>
-      <c r="R30" t="n">
-        <v>685</v>
-      </c>
-      <c r="S30" t="n">
-        <v>790</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3927</v>
-      </c>
-      <c r="U30" t="n">
-        <v>328</v>
-      </c>
-      <c r="V30" t="n">
-        <v>431</v>
-      </c>
-      <c r="W30" t="n">
-        <v>314</v>
-      </c>
-      <c r="X30" t="n">
-        <v>197</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1073</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1261</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0.851</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>268</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>631</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>107</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0.449</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>50</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>99</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>304</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>872</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0.349</v>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>7675:00</t>
-        </is>
-      </c>
-      <c r="AO30" t="n">
-        <v>3153.28</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0.598</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.016</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>1.581</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>4.947</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>6.528</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr"/>
+      <c r="BA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="inlineStr"/>
-      <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="inlineStr"/>
-      <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr"/>
-      <c r="AO31" t="inlineStr"/>
-      <c r="AP31" t="inlineStr"/>
-      <c r="AQ31" t="inlineStr"/>
-      <c r="AR31" t="inlineStr"/>
-      <c r="AS31" t="inlineStr"/>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AU31" t="inlineStr"/>
-      <c r="AV31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr"/>
-      <c r="AX31" t="inlineStr"/>
-      <c r="AY31" t="inlineStr"/>
-      <c r="AZ31" t="inlineStr"/>
-      <c r="BA31" t="inlineStr"/>
+          <t>#0 S. LARKIN (Per Game)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>12</v>
+      </c>
+      <c r="C31" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5.417</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5.417</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.083</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>201</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>3.833</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>5.167</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>29:51</t>
+        </is>
+      </c>
+      <c r="AO31" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0.178</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#0 S. LARKIN (Per Game)</t>
+          <t>#1 R. BEAUBOIS (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C32" t="n">
-        <v>15.25</v>
+        <v>3.857</v>
       </c>
       <c r="D32" t="n">
-        <v>2.75</v>
+        <v>1.036</v>
       </c>
       <c r="E32" t="n">
-        <v>5.417</v>
+        <v>1.821</v>
       </c>
       <c r="F32" t="n">
-        <v>2.333</v>
+        <v>0.536</v>
       </c>
       <c r="G32" t="n">
-        <v>5.417</v>
+        <v>1.5</v>
       </c>
       <c r="H32" t="n">
-        <v>2.75</v>
+        <v>0.179</v>
       </c>
       <c r="I32" t="n">
-        <v>3.083</v>
+        <v>0.179</v>
       </c>
       <c r="J32" t="n">
-        <v>4.167</v>
+        <v>0.821</v>
       </c>
       <c r="K32" t="n">
-        <v>1.833</v>
+        <v>0.857</v>
       </c>
       <c r="L32" t="n">
-        <v>0.5</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>0.333</v>
+        <v>0.429</v>
       </c>
       <c r="N32" t="n">
-        <v>0.75</v>
+        <v>0.214</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.5</v>
+        <v>0.357</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.417</v>
+        <v>0.357</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0.679</v>
       </c>
       <c r="S32" t="n">
-        <v>3.5</v>
+        <v>0.179</v>
       </c>
       <c r="T32" t="n">
-        <v>201</v>
+        <v>102</v>
       </c>
       <c r="U32" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.583</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.833</v>
+        <v>0.464</v>
       </c>
       <c r="Z32" t="n">
-        <v>5</v>
+        <v>0.536</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.767</v>
+        <v>0.867</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.5</v>
+        <v>0.714</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.417</v>
+        <v>1.143</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.621</v>
+        <v>0.625</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.167</v>
+        <v>0.036</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.75</v>
+        <v>0.321</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.222</v>
+        <v>0.111</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.083</v>
+        <v>0.107</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.25</v>
+        <v>0.357</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.25</v>
+        <v>0.429</v>
       </c>
       <c r="AL32" t="n">
-        <v>5.167</v>
+        <v>1.143</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.435</v>
+        <v>0.375</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>55:17</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>14.69</v>
+        <v>3.757</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.577</v>
+        <v>0.554</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.626</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.038</v>
+        <v>1.027</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.17</v>
+        <v>0.095</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.254</v>
+        <v>0.054</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.667</v>
+        <v>2.3</v>
       </c>
       <c r="AV32" t="n">
-        <v>4.333</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AW32" t="n">
-        <v>6</v>
+        <v>11.6</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.131</v>
+        <v>0.204</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.011</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.041</v>
+        <v>0.116</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.178</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#1 R. BEAUBOIS (Per Game)</t>
+          <t>#2 S. HAZER (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C33" t="n">
-        <v>3.857</v>
+        <v>5.314</v>
       </c>
       <c r="D33" t="n">
-        <v>1.036</v>
+        <v>1.4</v>
       </c>
       <c r="E33" t="n">
-        <v>1.821</v>
+        <v>2.943</v>
       </c>
       <c r="F33" t="n">
-        <v>0.536</v>
+        <v>0.514</v>
       </c>
       <c r="G33" t="n">
-        <v>1.5</v>
+        <v>1.743</v>
       </c>
       <c r="H33" t="n">
-        <v>0.179</v>
+        <v>0.971</v>
       </c>
       <c r="I33" t="n">
-        <v>0.179</v>
+        <v>1.286</v>
       </c>
       <c r="J33" t="n">
-        <v>0.821</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="R33" t="n">
         <v>0.857</v>
       </c>
-      <c r="L33" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0.679</v>
-      </c>
       <c r="S33" t="n">
-        <v>0.179</v>
+        <v>1.4</v>
       </c>
       <c r="T33" t="n">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="U33" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0.357</v>
+        <v>0.057</v>
       </c>
       <c r="X33" t="n">
-        <v>0.179</v>
+        <v>0.029</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.464</v>
+        <v>1.943</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.536</v>
+        <v>2.457</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.867</v>
+        <v>0.791</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.714</v>
+        <v>0.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.143</v>
+        <v>1.314</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.625</v>
+        <v>0.304</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.036</v>
+        <v>0.029</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.321</v>
+        <v>0.143</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.111</v>
+        <v>0.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.107</v>
+        <v>0.143</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.357</v>
+        <v>0.286</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.429</v>
+        <v>0.371</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.143</v>
+        <v>1.457</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.375</v>
+        <v>0.255</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>22:25</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>3.757</v>
+        <v>6.08</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.554</v>
+        <v>0.463</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.506</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.027</v>
+        <v>0.874</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.095</v>
+        <v>0.136</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.054</v>
+        <v>0.207</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.3</v>
+        <v>1.207</v>
       </c>
       <c r="AV33" t="n">
-        <v>9.300000000000001</v>
+        <v>5.655</v>
       </c>
       <c r="AW33" t="n">
-        <v>11.6</v>
+        <v>6.862</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.083</v>
+        <v>0.242</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.004</v>
+        <v>0.022</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.047</v>
+        <v>0.065</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.031</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#2 S. HAZER (Per Game)</t>
+          <t>#3 J. LOYD (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C34" t="n">
-        <v>5.314</v>
+        <v>11.382</v>
       </c>
       <c r="D34" t="n">
-        <v>1.4</v>
+        <v>1.882</v>
       </c>
       <c r="E34" t="n">
-        <v>2.943</v>
+        <v>4</v>
       </c>
       <c r="F34" t="n">
-        <v>0.514</v>
+        <v>1.588</v>
       </c>
       <c r="G34" t="n">
-        <v>1.743</v>
+        <v>4.588</v>
       </c>
       <c r="H34" t="n">
-        <v>0.971</v>
+        <v>2.853</v>
       </c>
       <c r="I34" t="n">
-        <v>1.286</v>
+        <v>3.324</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>1.853</v>
       </c>
       <c r="K34" t="n">
-        <v>0.657</v>
+        <v>1.882</v>
       </c>
       <c r="L34" t="n">
-        <v>0.229</v>
+        <v>0.618</v>
       </c>
       <c r="M34" t="n">
-        <v>0.343</v>
+        <v>0.618</v>
       </c>
       <c r="N34" t="n">
-        <v>0.229</v>
+        <v>0.382</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.829</v>
+        <v>1.235</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.771</v>
+        <v>1.118</v>
       </c>
       <c r="R34" t="n">
-        <v>0.857</v>
+        <v>2.176</v>
       </c>
       <c r="S34" t="n">
-        <v>1.4</v>
+        <v>3.882</v>
       </c>
       <c r="T34" t="n">
-        <v>154</v>
+        <v>395</v>
       </c>
       <c r="U34" t="n">
-        <v>0.629</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0.257</v>
+        <v>0.059</v>
       </c>
       <c r="X34" t="n">
-        <v>0.2</v>
+        <v>0.029</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.943</v>
+        <v>3.853</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.457</v>
+        <v>4.382</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.791</v>
+        <v>0.879</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.4</v>
+        <v>0.676</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.314</v>
+        <v>1.853</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.304</v>
+        <v>0.365</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.029</v>
+        <v>0.206</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.143</v>
+        <v>0.618</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.143</v>
+        <v>0.206</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.286</v>
+        <v>0.588</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.371</v>
+        <v>1.382</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.457</v>
+        <v>4</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.255</v>
+        <v>0.346</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>24:45</t>
+          <t>23:21</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>6.08</v>
+        <v>11.286</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.463</v>
+        <v>0.497</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.506</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.874</v>
+        <v>1.009</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.136</v>
+        <v>0.109</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.207</v>
+        <v>0.332</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.207</v>
+        <v>1.5</v>
       </c>
       <c r="AV34" t="n">
-        <v>5.655</v>
+        <v>6.952</v>
       </c>
       <c r="AW34" t="n">
-        <v>6.862</v>
+        <v>8.452</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.121</v>
+        <v>0.239</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.011</v>
+        <v>0.032</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.033</v>
+        <v>0.1</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.038</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#3 J. LOYD (Per Game)</t>
+          <t>#5 S. LEE (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C35" t="n">
-        <v>11.382</v>
+        <v>11.25</v>
       </c>
       <c r="D35" t="n">
-        <v>1.882</v>
+        <v>2.812</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>5.125</v>
       </c>
       <c r="F35" t="n">
-        <v>1.588</v>
+        <v>0.75</v>
       </c>
       <c r="G35" t="n">
-        <v>4.588</v>
+        <v>2.688</v>
       </c>
       <c r="H35" t="n">
-        <v>2.853</v>
+        <v>3.375</v>
       </c>
       <c r="I35" t="n">
-        <v>3.324</v>
+        <v>4.5</v>
       </c>
       <c r="J35" t="n">
-        <v>1.853</v>
+        <v>3.062</v>
       </c>
       <c r="K35" t="n">
-        <v>1.882</v>
+        <v>1.312</v>
       </c>
       <c r="L35" t="n">
-        <v>0.618</v>
+        <v>0.375</v>
       </c>
       <c r="M35" t="n">
-        <v>0.618</v>
+        <v>0.875</v>
       </c>
       <c r="N35" t="n">
-        <v>0.382</v>
+        <v>0.438</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.235</v>
+        <v>1.188</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.118</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="R35" t="n">
-        <v>2.176</v>
+        <v>1.312</v>
       </c>
       <c r="S35" t="n">
-        <v>3.882</v>
+        <v>3.75</v>
       </c>
       <c r="T35" t="n">
-        <v>395</v>
+        <v>211</v>
       </c>
       <c r="U35" t="n">
-        <v>1.029</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.471</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.294</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0.824</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>3.853</v>
+        <v>5.188</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.382</v>
+        <v>6.062</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.879</v>
+        <v>0.856</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.676</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.853</v>
+        <v>1.938</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.365</v>
+        <v>0.484</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.206</v>
+        <v>0.062</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.618</v>
+        <v>0.5</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.333</v>
+        <v>0.125</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.206</v>
+        <v>0.125</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.588</v>
+        <v>0.438</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.35</v>
+        <v>0.286</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.382</v>
+        <v>0.625</v>
       </c>
       <c r="AL35" t="n">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.346</v>
+        <v>0.278</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>45:19</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>11.286</v>
+        <v>10.98</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.497</v>
+        <v>0.504</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.574</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.009</v>
+        <v>1.025</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.109</v>
+        <v>0.108</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.332</v>
+        <v>0.432</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.5</v>
+        <v>2.579</v>
       </c>
       <c r="AV35" t="n">
-        <v>6.952</v>
+        <v>6.579</v>
       </c>
       <c r="AW35" t="n">
-        <v>8.452</v>
+        <v>9.157999999999999</v>
       </c>
       <c r="AX35" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="BA35" t="n">
         <v>0.123</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>0.074</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#5 S. LEE (Per Game)</t>
+          <t>#6 R. FENEMEN (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>11.25</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>2.812</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>5.125</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>2.688</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>3.375</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>3.062</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>1.312</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0.438</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.188</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.9379999999999999</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.312</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0.8120000000000001</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.375</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0.8120000000000001</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>5.188</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>6.062</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.856</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.9379999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.938</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.484</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.438</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.278</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>42:22</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>10.98</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.504</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.574</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.025</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.108</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.432</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.579</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>6.579</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>9.157999999999999</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.128</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#6 R. FENEMEN (Per Game)</t>
+          <t>#8 N. WEILER-BABB (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1.053</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>2.184</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1.368</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>3.737</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1.289</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1.711</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>4.684</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>2.553</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>0.737</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1.184</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>0.184</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.553</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.395</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.158</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>423</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>0.079</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.947</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.289</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>0.851</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>0.342</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>0.868</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>0.394</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>0.316</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.342</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>3.579</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>27:46</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>8.226000000000001</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>0.524</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>0.912</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>0.189</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>0.218</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>3.017</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>3.814</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>6.831</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>0.114</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#8 N. WEILER-BABB (Per Game)</t>
+          <t>#9 G. PAPAGIANNIS (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="C38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T38" t="n">
+        <v>27</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AO38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV38" t="n">
         <v>7.5</v>
       </c>
-      <c r="D38" t="n">
-        <v>1.053</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2.184</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1.368</v>
-      </c>
-      <c r="G38" t="n">
-        <v>3.737</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1.289</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1.711</v>
-      </c>
-      <c r="J38" t="n">
-        <v>4.684</v>
-      </c>
-      <c r="K38" t="n">
-        <v>2.553</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0.737</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1.184</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.553</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.526</v>
-      </c>
-      <c r="R38" t="n">
-        <v>2.395</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.158</v>
-      </c>
-      <c r="T38" t="n">
-        <v>423</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0.658</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.947</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.289</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0.851</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0.868</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0.394</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1.342</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>3.579</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>54:18</t>
-        </is>
-      </c>
-      <c r="AO38" t="n">
-        <v>8.226000000000001</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>0.912</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0.189</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0.218</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>3.017</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>3.814</v>
-      </c>
       <c r="AW38" t="n">
-        <v>6.831</v>
+        <v>10</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.075</v>
+        <v>0.114</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.016</v>
+        <v>0.082</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.058</v>
+        <v>0.201</v>
       </c>
       <c r="BA38" t="n">
-        <v>0.18</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#9 G. PAPAGIANNIS (Per Game)</t>
+          <t>#10 I. CORDINIER (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C39" t="n">
-        <v>2.2</v>
+        <v>9.4</v>
       </c>
       <c r="D39" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>3.867</v>
       </c>
       <c r="F39" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.933</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.467</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.433</v>
+      </c>
+      <c r="T39" t="n">
+        <v>287</v>
+      </c>
+      <c r="U39" t="n">
         <v>0.2</v>
       </c>
-      <c r="G39" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1</v>
-      </c>
-      <c r="M39" t="n">
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.767</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.867</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AG39" t="n">
         <v>0.4</v>
       </c>
-      <c r="N39" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1</v>
-      </c>
-      <c r="S39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T39" t="n">
-        <v>27</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>0.238</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.2</v>
+        <v>0.867</v>
       </c>
       <c r="AL39" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>26:49</t>
+          <t>24:02</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>3.4</v>
+        <v>9.933</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.367</v>
+        <v>0.495</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.367</v>
+        <v>0.555</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.647</v>
+        <v>0.946</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.118</v>
+        <v>0.148</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>0.285</v>
       </c>
       <c r="AU39" t="n">
-        <v>2.5</v>
+        <v>1.318</v>
       </c>
       <c r="AV39" t="n">
-        <v>7.5</v>
+        <v>5.023</v>
       </c>
       <c r="AW39" t="n">
-        <v>10</v>
+        <v>6.341</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.063</v>
+        <v>0.204</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.045</v>
+        <v>0.03</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0.111</v>
+        <v>0.115</v>
       </c>
       <c r="BA39" t="n">
-        <v>0.036</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#10 I. CORDINIER (Per Game)</t>
+          <t>#11 R. SMITS (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C40" t="n">
-        <v>9.4</v>
+        <v>6.657</v>
       </c>
       <c r="D40" t="n">
-        <v>2.1</v>
+        <v>1.829</v>
       </c>
       <c r="E40" t="n">
-        <v>3.867</v>
+        <v>2.943</v>
       </c>
       <c r="F40" t="n">
-        <v>1.033</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>3.5</v>
+        <v>2.086</v>
       </c>
       <c r="H40" t="n">
-        <v>2.1</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>1.286</v>
       </c>
       <c r="J40" t="n">
-        <v>1.933</v>
+        <v>0.743</v>
       </c>
       <c r="K40" t="n">
-        <v>2.233</v>
+        <v>2.114</v>
       </c>
       <c r="L40" t="n">
-        <v>0.6</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>0.767</v>
+        <v>0.343</v>
       </c>
       <c r="N40" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.314</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T40" t="n">
+        <v>233</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.229</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.771</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.804</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>0.533</v>
       </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1.467</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R40" t="n">
-        <v>2.233</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.433</v>
-      </c>
-      <c r="T40" t="n">
-        <v>287</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.767</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0.876</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.867</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0.238</v>
-      </c>
       <c r="AK40" t="n">
-        <v>0.867</v>
+        <v>0.457</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.8</v>
+        <v>1.657</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.31</v>
+        <v>0.276</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>49:00</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>9.933</v>
+        <v>6.394</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.495</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.555</v>
+        <v>0.595</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.946</v>
+        <v>1.041</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.148</v>
+        <v>0.125</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.285</v>
+        <v>0.188</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.318</v>
+        <v>0.929</v>
       </c>
       <c r="AV40" t="n">
-        <v>5.023</v>
+        <v>6.286</v>
       </c>
       <c r="AW40" t="n">
-        <v>6.341</v>
+        <v>7.214</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.1</v>
+        <v>0.168</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.015</v>
+        <v>0.061</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0.056</v>
+        <v>0.139</v>
       </c>
       <c r="BA40" t="n">
-        <v>0.076</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#11 R. SMITS (Per Game)</t>
+          <t>#13 B. DESSERT (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C41" t="n">
-        <v>6.657</v>
+        <v>4.737</v>
       </c>
       <c r="D41" t="n">
-        <v>1.829</v>
+        <v>2.158</v>
       </c>
       <c r="E41" t="n">
-        <v>2.943</v>
+        <v>3.158</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6860000000000001</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>2.086</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.421</v>
       </c>
       <c r="I41" t="n">
-        <v>1.286</v>
+        <v>0.789</v>
       </c>
       <c r="J41" t="n">
-        <v>0.743</v>
+        <v>0.316</v>
       </c>
       <c r="K41" t="n">
-        <v>2.114</v>
+        <v>1.053</v>
       </c>
       <c r="L41" t="n">
-        <v>0.9429999999999999</v>
+        <v>1.211</v>
       </c>
       <c r="M41" t="n">
-        <v>0.343</v>
+        <v>0.368</v>
       </c>
       <c r="N41" t="n">
-        <v>0.229</v>
+        <v>0.842</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.8</v>
+        <v>0.789</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.8</v>
+        <v>0.737</v>
       </c>
       <c r="R41" t="n">
-        <v>2.314</v>
+        <v>1.263</v>
       </c>
       <c r="S41" t="n">
-        <v>1.6</v>
+        <v>0.737</v>
       </c>
       <c r="T41" t="n">
-        <v>233</v>
+        <v>111</v>
       </c>
       <c r="U41" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.316</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.053</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AO41" t="n">
+        <v>4.295</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.103</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="AU41" t="n">
         <v>0.4</v>
       </c>
-      <c r="X41" t="n">
-        <v>0.229</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>2.229</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.771</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0.804</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0.457</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0.457</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0.229</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>0.457</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>1.657</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>37:31</t>
-        </is>
-      </c>
-      <c r="AO41" t="n">
-        <v>6.394</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.041</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>0.929</v>
-      </c>
       <c r="AV41" t="n">
-        <v>6.286</v>
+        <v>4</v>
       </c>
       <c r="AW41" t="n">
-        <v>7.214</v>
+        <v>4.4</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.184</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.03</v>
+        <v>0.127</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.113</v>
       </c>
       <c r="BA41" t="n">
-        <v>0.029</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#13 B. DESSERT (Per Game)</t>
+          <t>#15 P. DOZIER (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C42" t="n">
-        <v>4.737</v>
+        <v>9.692</v>
       </c>
       <c r="D42" t="n">
-        <v>2.158</v>
+        <v>2.423</v>
       </c>
       <c r="E42" t="n">
-        <v>3.158</v>
+        <v>6.038</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1.231</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>3.654</v>
       </c>
       <c r="H42" t="n">
-        <v>0.421</v>
+        <v>1.154</v>
       </c>
       <c r="I42" t="n">
-        <v>0.789</v>
+        <v>1.615</v>
       </c>
       <c r="J42" t="n">
-        <v>0.316</v>
+        <v>2.5</v>
       </c>
       <c r="K42" t="n">
-        <v>1.053</v>
+        <v>1.808</v>
       </c>
       <c r="L42" t="n">
-        <v>1.211</v>
+        <v>0.615</v>
       </c>
       <c r="M42" t="n">
-        <v>0.368</v>
+        <v>1.038</v>
       </c>
       <c r="N42" t="n">
-        <v>0.842</v>
+        <v>0.654</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.789</v>
+        <v>1.577</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.737</v>
+        <v>1.5</v>
       </c>
       <c r="R42" t="n">
-        <v>1.263</v>
+        <v>2.192</v>
       </c>
       <c r="S42" t="n">
-        <v>0.737</v>
+        <v>2.269</v>
       </c>
       <c r="T42" t="n">
-        <v>111</v>
+        <v>216</v>
       </c>
       <c r="U42" t="n">
-        <v>0.421</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.158</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0.421</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.316</v>
+        <v>2.038</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.053</v>
+        <v>2.731</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.759</v>
+        <v>0.746</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.263</v>
+        <v>1.077</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.526</v>
+        <v>3.231</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>0.462</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.231</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>0.462</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>0.571</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>0.769</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>2.846</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>4.295</v>
+        <v>11.98</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.676</v>
+        <v>0.466</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.103</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.184</v>
+        <v>0.132</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.133</v>
+        <v>0.119</v>
       </c>
       <c r="AU42" t="n">
-        <v>0.4</v>
+        <v>1.585</v>
       </c>
       <c r="AV42" t="n">
-        <v>4</v>
+        <v>6.146</v>
       </c>
       <c r="AW42" t="n">
-        <v>4.4</v>
+        <v>7.732</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.094</v>
+        <v>0.272</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.065</v>
+        <v>0.034</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0.058</v>
+        <v>0.103</v>
       </c>
       <c r="BA42" t="n">
-        <v>0.012</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#15 P. DOZIER (Per Game)</t>
+          <t>#17 V. POIRIER (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C43" t="n">
-        <v>9.692</v>
+        <v>8</v>
       </c>
       <c r="D43" t="n">
-        <v>2.423</v>
+        <v>3.143</v>
       </c>
       <c r="E43" t="n">
-        <v>6.038</v>
+        <v>6</v>
       </c>
       <c r="F43" t="n">
-        <v>1.231</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>3.654</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.154</v>
+        <v>1.714</v>
       </c>
       <c r="I43" t="n">
-        <v>1.615</v>
+        <v>2.286</v>
       </c>
       <c r="J43" t="n">
-        <v>2.5</v>
+        <v>1.214</v>
       </c>
       <c r="K43" t="n">
-        <v>1.808</v>
+        <v>2.571</v>
       </c>
       <c r="L43" t="n">
-        <v>0.615</v>
+        <v>2.071</v>
       </c>
       <c r="M43" t="n">
-        <v>1.038</v>
+        <v>0.5</v>
       </c>
       <c r="N43" t="n">
-        <v>0.654</v>
+        <v>0.857</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.577</v>
+        <v>0.714</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.5</v>
+        <v>0.714</v>
       </c>
       <c r="R43" t="n">
-        <v>2.192</v>
+        <v>1.786</v>
       </c>
       <c r="S43" t="n">
-        <v>2.269</v>
+        <v>2.357</v>
       </c>
       <c r="T43" t="n">
-        <v>216</v>
+        <v>163</v>
       </c>
       <c r="U43" t="n">
-        <v>0.846</v>
+        <v>0.143</v>
       </c>
       <c r="V43" t="n">
-        <v>0.769</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0.231</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0.154</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.038</v>
+        <v>4</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.731</v>
+        <v>5.143</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.746</v>
+        <v>0.778</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.077</v>
+        <v>0.857</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.231</v>
+        <v>2.214</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.333</v>
+        <v>0.387</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.231</v>
+        <v>0.357</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.8080000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AO43" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="AQ43" t="n">
         <v>0.571</v>
       </c>
-      <c r="AK43" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>2.846</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>43:55</t>
-        </is>
-      </c>
-      <c r="AO43" t="n">
-        <v>11.98</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>0.466</v>
-      </c>
       <c r="AR43" t="n">
-        <v>0.8090000000000001</v>
+        <v>1.036</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.132</v>
+        <v>0.093</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.119</v>
+        <v>0.286</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.585</v>
+        <v>1.7</v>
       </c>
       <c r="AV43" t="n">
-        <v>6.146</v>
+        <v>8.4</v>
       </c>
       <c r="AW43" t="n">
-        <v>7.732</v>
+        <v>10.1</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.135</v>
+        <v>0.21</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.017</v>
+        <v>0.138</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0.051</v>
+        <v>0.175</v>
       </c>
       <c r="BA43" t="n">
-        <v>0.101</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#17 V. POIRIER (Per Game)</t>
+          <t>#19 B. YILDIZLI (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>3.143</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -7281,79 +7281,79 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.714</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>2.286</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>2.571</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>2.071</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>0.857</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0.714</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.714</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.786</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>2.357</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0.643</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0.357</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>5.143</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.778</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.857</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.214</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.387</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.357</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -7378,111 +7378,111 @@
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>34:14</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>7.72</v>
+        <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.524</v>
+        <v>0</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.036</v>
+        <v>0</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.093</v>
+        <v>0</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.073</v>
+        <v>0</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0.093</v>
+        <v>0</v>
       </c>
       <c r="BA44" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>#19 B. YILDIZLI (Per Game)</t>
+          <t>#21 C. SWIDER (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>4.444</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>0.389</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>0.639</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1.056</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>2.194</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>0.528</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.028</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>0.306</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -7497,688 +7497,688 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>0.722</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>0.778</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>0.929</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>0.361</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>0.694</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1.639</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>0.424</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>0.696</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>0.725</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>1.363</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>0.176</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>1.143</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>14.571</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>15.714</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>0.215</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>#21 C. SWIDER (Per Game)</t>
+          <t>#23 D. MUTAF (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C46" t="n">
-        <v>4.444</v>
+        <v>1.3</v>
       </c>
       <c r="D46" t="n">
-        <v>0.389</v>
+        <v>0.25</v>
       </c>
       <c r="E46" t="n">
-        <v>0.639</v>
+        <v>0.45</v>
       </c>
       <c r="F46" t="n">
-        <v>1.056</v>
+        <v>0.25</v>
       </c>
       <c r="G46" t="n">
-        <v>2.194</v>
+        <v>0.55</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="I46" t="n">
-        <v>0.528</v>
+        <v>0.1</v>
       </c>
       <c r="J46" t="n">
-        <v>0.222</v>
+        <v>0.2</v>
       </c>
       <c r="K46" t="n">
-        <v>0.75</v>
+        <v>0.05</v>
       </c>
       <c r="L46" t="n">
-        <v>0.139</v>
+        <v>0.05</v>
       </c>
       <c r="M46" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0.056</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.194</v>
+        <v>0.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.194</v>
+        <v>0.15</v>
       </c>
       <c r="R46" t="n">
-        <v>1.028</v>
+        <v>0.4</v>
       </c>
       <c r="S46" t="n">
-        <v>0.306</v>
+        <v>0.05</v>
       </c>
       <c r="T46" t="n">
-        <v>124</v>
+        <v>11</v>
       </c>
       <c r="U46" t="n">
-        <v>0.528</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0.611</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0.278</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.722</v>
+        <v>0.15</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.778</v>
+        <v>0.15</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.929</v>
+        <v>1</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.111</v>
+        <v>0.05</v>
       </c>
       <c r="AC46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD46" t="n">
         <v>0.25</v>
       </c>
-      <c r="AD46" t="n">
-        <v>0.444</v>
-      </c>
       <c r="AE46" t="n">
-        <v>0.056</v>
+        <v>0.1</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.111</v>
+        <v>0.15</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.361</v>
+        <v>0.15</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.556</v>
+        <v>0.25</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.694</v>
+        <v>0.1</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.639</v>
+        <v>0.3</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.424</v>
+        <v>0.333</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>02:29</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>3.26</v>
+        <v>1.194</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.696</v>
+        <v>0.625</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.725</v>
+        <v>0.623</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.363</v>
+        <v>1.089</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.06</v>
+        <v>0.126</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.176</v>
+        <v>0.05</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.143</v>
+        <v>1.333</v>
       </c>
       <c r="AV46" t="n">
-        <v>14.571</v>
+        <v>6.667</v>
       </c>
       <c r="AW46" t="n">
-        <v>15.714</v>
+        <v>8</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.237</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.024</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0.05</v>
+        <v>0.025</v>
       </c>
       <c r="BA46" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>#23 D. MUTAF (Per Game)</t>
+          <t>#24 E. OSMANI (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C47" t="n">
-        <v>1.3</v>
+        <v>10.861</v>
       </c>
       <c r="D47" t="n">
-        <v>0.25</v>
+        <v>3.083</v>
       </c>
       <c r="E47" t="n">
-        <v>0.45</v>
+        <v>5.389</v>
       </c>
       <c r="F47" t="n">
-        <v>0.25</v>
+        <v>1.028</v>
       </c>
       <c r="G47" t="n">
-        <v>0.55</v>
+        <v>2.528</v>
       </c>
       <c r="H47" t="n">
-        <v>0.05</v>
+        <v>1.611</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1</v>
+        <v>2.056</v>
       </c>
       <c r="J47" t="n">
-        <v>0.2</v>
+        <v>1.333</v>
       </c>
       <c r="K47" t="n">
-        <v>0.05</v>
+        <v>3.389</v>
       </c>
       <c r="L47" t="n">
-        <v>0.05</v>
+        <v>1.222</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.15</v>
+        <v>2.028</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.15</v>
+        <v>1.833</v>
       </c>
       <c r="R47" t="n">
-        <v>0.4</v>
+        <v>1.972</v>
       </c>
       <c r="S47" t="n">
-        <v>0.05</v>
+        <v>2.833</v>
       </c>
       <c r="T47" t="n">
-        <v>11</v>
+        <v>444</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.15</v>
+        <v>3.472</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.15</v>
+        <v>4.333</v>
       </c>
       <c r="AA47" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.389</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="AJ47" t="n">
         <v>1</v>
       </c>
-      <c r="AB47" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0.6</v>
-      </c>
       <c r="AK47" t="n">
-        <v>0.1</v>
+        <v>0.944</v>
       </c>
       <c r="AL47" t="n">
-        <v>0.3</v>
+        <v>2.444</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.333</v>
+        <v>0.386</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>04:59</t>
+          <t>24:17</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>1.194</v>
+        <v>10.849</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.625</v>
+        <v>0.584</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.623</v>
+        <v>0.616</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.089</v>
+        <v>1.001</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.126</v>
+        <v>0.187</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.05</v>
+        <v>0.204</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.333</v>
+        <v>0.658</v>
       </c>
       <c r="AV47" t="n">
-        <v>6.667</v>
+        <v>3.904</v>
       </c>
       <c r="AW47" t="n">
-        <v>8</v>
+        <v>4.562</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.118</v>
+        <v>0.221</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.012</v>
+        <v>0.061</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0.012</v>
+        <v>0.172</v>
       </c>
       <c r="BA47" t="n">
-        <v>0.007</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>#24 E. OSMANI (Per Game)</t>
+          <t>#33 E. YILMAZ (Per Game)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C48" t="n">
-        <v>10.861</v>
+        <v>0.848</v>
       </c>
       <c r="D48" t="n">
-        <v>3.083</v>
+        <v>0.182</v>
       </c>
       <c r="E48" t="n">
-        <v>5.389</v>
+        <v>0.303</v>
       </c>
       <c r="F48" t="n">
-        <v>1.028</v>
+        <v>0.03</v>
       </c>
       <c r="G48" t="n">
-        <v>2.528</v>
+        <v>0.364</v>
       </c>
       <c r="H48" t="n">
-        <v>1.611</v>
+        <v>0.394</v>
       </c>
       <c r="I48" t="n">
-        <v>2.056</v>
+        <v>0.576</v>
       </c>
       <c r="J48" t="n">
-        <v>1.333</v>
+        <v>0.364</v>
       </c>
       <c r="K48" t="n">
-        <v>3.389</v>
+        <v>0.848</v>
       </c>
       <c r="L48" t="n">
-        <v>1.222</v>
+        <v>0.242</v>
       </c>
       <c r="M48" t="n">
-        <v>0.5</v>
+        <v>0.394</v>
       </c>
       <c r="N48" t="n">
-        <v>0.444</v>
+        <v>0.152</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.028</v>
+        <v>0.364</v>
       </c>
       <c r="Q48" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="T48" t="n">
+        <v>42</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AN48" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="AO48" t="n">
+        <v>1.284</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV48" t="n">
         <v>1.833</v>
       </c>
-      <c r="R48" t="n">
-        <v>1.972</v>
-      </c>
-      <c r="S48" t="n">
+      <c r="AW48" t="n">
         <v>2.833</v>
       </c>
-      <c r="T48" t="n">
-        <v>444</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0.722</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>3.472</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0.801</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.139</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>2.389</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0.477</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0.278</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>0.944</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>2.444</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>0.386</v>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>45:11</t>
-        </is>
-      </c>
-      <c r="AO48" t="n">
-        <v>10.849</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>0.616</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>0.658</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>3.904</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>4.562</v>
-      </c>
       <c r="AX48" t="n">
-        <v>0.119</v>
+        <v>0.103</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.033</v>
+        <v>0.048</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0.093</v>
+        <v>0.17</v>
       </c>
       <c r="BA48" t="n">
-        <v>0.055</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>#33 E. YILMAZ (Per Game)</t>
+          <t>#88 K. JONES (Per Game)</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C49" t="n">
-        <v>0.848</v>
+        <v>3.514</v>
       </c>
       <c r="D49" t="n">
-        <v>0.182</v>
+        <v>1.568</v>
       </c>
       <c r="E49" t="n">
-        <v>0.303</v>
+        <v>1.703</v>
       </c>
       <c r="F49" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.364</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.394</v>
+        <v>0.378</v>
       </c>
       <c r="I49" t="n">
-        <v>0.576</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>0.364</v>
+        <v>0.459</v>
       </c>
       <c r="K49" t="n">
-        <v>0.848</v>
+        <v>2.324</v>
       </c>
       <c r="L49" t="n">
-        <v>0.242</v>
+        <v>1.108</v>
       </c>
       <c r="M49" t="n">
-        <v>0.394</v>
+        <v>0.514</v>
       </c>
       <c r="N49" t="n">
-        <v>0.152</v>
+        <v>1.216</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0.364</v>
+        <v>0.459</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.364</v>
+        <v>0.405</v>
       </c>
       <c r="R49" t="n">
-        <v>1</v>
+        <v>1.541</v>
       </c>
       <c r="S49" t="n">
-        <v>0.424</v>
+        <v>0.514</v>
       </c>
       <c r="T49" t="n">
-        <v>42</v>
+        <v>271</v>
       </c>
       <c r="U49" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>0.121</v>
+        <v>0.054</v>
       </c>
       <c r="W49" t="n">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.515</v>
+        <v>1.919</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.545</v>
+        <v>1.946</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.944</v>
+        <v>0.986</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.061</v>
+        <v>0.027</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.152</v>
+        <v>0.108</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -8187,82 +8187,82 @@
         <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.091</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="n">
         <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>1.284</v>
+        <v>2.412</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.341</v>
+        <v>0.921</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.461</v>
+        <v>0.9</v>
       </c>
       <c r="AR49" t="n">
-        <v>0.661</v>
+        <v>1.457</v>
       </c>
       <c r="AS49" t="n">
-        <v>0.283</v>
+        <v>0.19</v>
       </c>
       <c r="AT49" t="n">
-        <v>0.591</v>
+        <v>0.222</v>
       </c>
       <c r="AU49" t="n">
         <v>1</v>
       </c>
       <c r="AV49" t="n">
-        <v>1.833</v>
+        <v>3.706</v>
       </c>
       <c r="AW49" t="n">
-        <v>2.833</v>
+        <v>4.706</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.051</v>
+        <v>0.079</v>
       </c>
       <c r="AY49" t="n">
-        <v>0.024</v>
+        <v>0.089</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.191</v>
       </c>
       <c r="BA49" t="n">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>#88 K. JONES (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C50" t="n">
-        <v>3.514</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>1.568</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1.703</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -8271,79 +8271,79 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.378</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5679999999999999</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0.459</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>2.324</v>
+        <v>1.711</v>
       </c>
       <c r="L50" t="n">
-        <v>1.108</v>
+        <v>1.658</v>
       </c>
       <c r="M50" t="n">
-        <v>0.514</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1.216</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0.459</v>
+        <v>0.921</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.405</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.541</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.514</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>0.5679999999999999</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>0.432</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>0.324</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0.216</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.919</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.946</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.986</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.108</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -8368,209 +8368,209 @@
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>32:23</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>2.412</v>
+        <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.921</v>
+        <v>0</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.457</v>
+        <v>0</v>
       </c>
       <c r="AS50" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="AT50" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="AU50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV50" t="n">
-        <v>3.706</v>
+        <v>0</v>
       </c>
       <c r="AW50" t="n">
-        <v>4.706</v>
+        <v>0</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="AY50" t="n">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="BA50" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>38</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>80.105</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>19.289</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>35.5</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>9.157999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>25.789</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>14.053</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>17.921</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>17.474</v>
       </c>
       <c r="K51" t="n">
-        <v>1.711</v>
+        <v>22</v>
       </c>
       <c r="L51" t="n">
+        <v>9.395</v>
+      </c>
+      <c r="M51" t="n">
+        <v>6.368</v>
+      </c>
+      <c r="N51" t="n">
+        <v>5</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>12.526</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>10.816</v>
+      </c>
+      <c r="R51" t="n">
+        <v>18.737</v>
+      </c>
+      <c r="S51" t="n">
+        <v>19.947</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3508</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>26.079</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>31.263</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>6.211</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>14.789</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="AH51" t="n">
         <v>1.658</v>
       </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0.921</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>3.789</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>0.438</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>0.341</v>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>201:58</t>
         </is>
       </c>
       <c r="AO51" t="n">
-        <v>0</v>
+        <v>81.70099999999999</v>
       </c>
       <c r="AP51" t="n">
-        <v>0</v>
+        <v>0.539</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="AR51" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AS51" t="n">
-        <v>0</v>
+        <v>0.153</v>
       </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>0.229</v>
       </c>
       <c r="AU51" t="n">
-        <v>0</v>
+        <v>1.395</v>
       </c>
       <c r="AV51" t="n">
-        <v>0</v>
+        <v>4.893</v>
       </c>
       <c r="AW51" t="n">
-        <v>0</v>
+        <v>6.288</v>
       </c>
       <c r="AX51" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY51" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="BA51" t="n">
         <v>0</v>
@@ -8579,495 +8579,165 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>38</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>84.342</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>19.842</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>35.895</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>9.316000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>25.553</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>16.711</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>20.711</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>19.632</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>23.895</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>10.684</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>5.737</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>12.421</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>11.211</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>18.026</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>20.789</v>
       </c>
       <c r="T52" t="n">
-        <v>93</v>
+        <v>3927</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>0.263</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>0.421</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>0.474</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>0.289</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>28.237</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>33.184</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>0.851</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>7.053</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>16.605</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>0.425</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.263</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>2.816</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>0.449</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.316</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>2.605</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>0.505</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>22.947</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>0.349</v>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>201:58</t>
         </is>
       </c>
       <c r="AO52" t="n">
-        <v>0.921</v>
+        <v>82.98099999999999</v>
       </c>
       <c r="AP52" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0</v>
+        <v>0.598</v>
       </c>
       <c r="AR52" t="n">
-        <v>0</v>
+        <v>1.016</v>
       </c>
       <c r="AS52" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>0.272</v>
       </c>
       <c r="AU52" t="n">
-        <v>0</v>
+        <v>1.581</v>
       </c>
       <c r="AV52" t="n">
-        <v>0</v>
+        <v>4.947</v>
       </c>
       <c r="AW52" t="n">
-        <v>0</v>
+        <v>6.528</v>
       </c>
       <c r="AX52" t="n">
-        <v>0</v>
+        <v>0.203</v>
       </c>
       <c r="AY52" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="BA52" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>38</v>
-      </c>
-      <c r="C53" t="n">
-        <v>80.105</v>
-      </c>
-      <c r="D53" t="n">
-        <v>19.289</v>
-      </c>
-      <c r="E53" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="F53" t="n">
-        <v>9.157999999999999</v>
-      </c>
-      <c r="G53" t="n">
-        <v>25.789</v>
-      </c>
-      <c r="H53" t="n">
-        <v>14.053</v>
-      </c>
-      <c r="I53" t="n">
-        <v>17.921</v>
-      </c>
-      <c r="J53" t="n">
-        <v>17.474</v>
-      </c>
-      <c r="K53" t="n">
-        <v>22</v>
-      </c>
-      <c r="L53" t="n">
-        <v>9.395</v>
-      </c>
-      <c r="M53" t="n">
-        <v>6.368</v>
-      </c>
-      <c r="N53" t="n">
-        <v>5</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>12.526</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>10.842</v>
-      </c>
-      <c r="R53" t="n">
-        <v>18.737</v>
-      </c>
-      <c r="S53" t="n">
-        <v>19.947</v>
-      </c>
-      <c r="T53" t="n">
-        <v>3508</v>
-      </c>
-      <c r="U53" t="n">
-        <v>8.157999999999999</v>
-      </c>
-      <c r="V53" t="n">
-        <v>10.026</v>
-      </c>
-      <c r="W53" t="n">
-        <v>6.026</v>
-      </c>
-      <c r="X53" t="n">
-        <v>3.868</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>26.079</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>31.263</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0.834</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>6.211</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>14.789</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>1.053</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0.301</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.658</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>3.789</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>22</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>201:58</t>
-        </is>
-      </c>
-      <c r="AO53" t="n">
-        <v>81.70099999999999</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>0.539</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>0.229</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>1.395</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>4.893</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>6.288</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="BA53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>38</v>
-      </c>
-      <c r="C54" t="n">
-        <v>84.342</v>
-      </c>
-      <c r="D54" t="n">
-        <v>19.842</v>
-      </c>
-      <c r="E54" t="n">
-        <v>35.895</v>
-      </c>
-      <c r="F54" t="n">
-        <v>9.316000000000001</v>
-      </c>
-      <c r="G54" t="n">
-        <v>25.553</v>
-      </c>
-      <c r="H54" t="n">
-        <v>16.711</v>
-      </c>
-      <c r="I54" t="n">
-        <v>20.711</v>
-      </c>
-      <c r="J54" t="n">
-        <v>19.632</v>
-      </c>
-      <c r="K54" t="n">
-        <v>23.895</v>
-      </c>
-      <c r="L54" t="n">
-        <v>10.684</v>
-      </c>
-      <c r="M54" t="n">
-        <v>5.737</v>
-      </c>
-      <c r="N54" t="n">
-        <v>5</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>12.421</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>11.237</v>
-      </c>
-      <c r="R54" t="n">
-        <v>18.026</v>
-      </c>
-      <c r="S54" t="n">
-        <v>20.789</v>
-      </c>
-      <c r="T54" t="n">
-        <v>3927</v>
-      </c>
-      <c r="U54" t="n">
-        <v>8.632</v>
-      </c>
-      <c r="V54" t="n">
-        <v>11.342</v>
-      </c>
-      <c r="W54" t="n">
-        <v>8.263</v>
-      </c>
-      <c r="X54" t="n">
-        <v>5.184</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>28.237</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>33.184</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0.851</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>7.053</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>16.605</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1.263</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>2.816</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>0.449</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.316</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>2.605</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>8</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>22.947</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>0.349</v>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>201:58</t>
-        </is>
-      </c>
-      <c r="AO54" t="n">
-        <v>82.98099999999999</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>0.598</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>1.016</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>1.581</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>4.947</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>6.528</v>
-      </c>
-      <c r="AX54" t="n">
-        <v>0.203</v>
-      </c>
-      <c r="AY54" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="BA54" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_ANADOLU EFES ISTANBUL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_ANADOLU EFES ISTANBUL.xlsx
@@ -671,13 +671,13 @@
         <v>0.2292829540575354</v>
       </c>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>326</v>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>384</v>
       </c>
       <c r="L2" t="n">
-        <v>9</v>
+        <v>237</v>
       </c>
       <c r="M2" t="n">
         <v>411</v>
@@ -752,13 +752,13 @@
         <v>1.065306122448979</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.02542372881355932</v>
+        <v>0.690677966101695</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.02521008403361345</v>
+        <v>1.07563025210084</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.25</v>
+        <v>1.529032258064516</v>
       </c>
       <c r="AN2" t="n">
         <v>1.394957983193277</v>
@@ -801,13 +801,13 @@
         <v>0.2292829540575354</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3157894736842105</v>
+        <v>8.578947368421053</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2368421052631579</v>
+        <v>10.10526315789474</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2368421052631579</v>
+        <v>6.236842105263158</v>
       </c>
       <c r="M3" t="n">
         <v>10.81578947368421</v>
@@ -882,13 +882,13 @@
         <v>1.06530612244898</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.02542372881355932</v>
+        <v>0.690677966101695</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.02521008403361344</v>
+        <v>1.07563025210084</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.25</v>
+        <v>1.529032258064516</v>
       </c>
       <c r="AN3" t="n">
         <v>1.394957983193277</v>
@@ -931,13 +931,13 @@
         <v>0.271948608137045</v>
       </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>356</v>
       </c>
       <c r="K4" t="n">
-        <v>16</v>
+        <v>436</v>
       </c>
       <c r="L4" t="n">
-        <v>18</v>
+        <v>321</v>
       </c>
       <c r="M4" t="n">
         <v>426</v>
@@ -1012,13 +1012,13 @@
         <v>1.093717816683831</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.02100840336134454</v>
+        <v>0.7478991596638656</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.03940886699507389</v>
+        <v>1.073891625615764</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.636363636363636</v>
+        <v>1.573529411764706</v>
       </c>
       <c r="AN4" t="n">
         <v>1.580508474576271</v>
@@ -1061,13 +1061,13 @@
         <v>0.271948608137045</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2631578947368421</v>
+        <v>9.368421052631579</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4210526315789473</v>
+        <v>11.47368421052632</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4736842105263158</v>
+        <v>8.447368421052632</v>
       </c>
       <c r="M5" t="n">
         <v>11.21052631578947</v>
@@ -1142,13 +1142,13 @@
         <v>1.093717816683831</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.02100840336134454</v>
+        <v>0.7478991596638654</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.03940886699507389</v>
+        <v>1.073891625615764</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.636363636363636</v>
+        <v>1.573529411764706</v>
       </c>
       <c r="AN5" t="n">
         <v>1.580508474576271</v>
@@ -1486,16 +1486,16 @@
         <v>201</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="V8" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y8" t="n">
         <v>46</v>
@@ -1651,16 +1651,16 @@
         <v>102</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="n">
         <v>13</v>
@@ -1816,16 +1816,16 @@
         <v>154</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y10" t="n">
         <v>68</v>
@@ -1981,16 +1981,16 @@
         <v>395</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Y11" t="n">
         <v>131</v>
@@ -2146,16 +2146,16 @@
         <v>211</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y12" t="n">
         <v>83</v>
@@ -2476,16 +2476,16 @@
         <v>423</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="W14" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Y14" t="n">
         <v>74</v>
@@ -2644,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2806,16 +2806,16 @@
         <v>287</v>
       </c>
       <c r="U16" t="n">
+        <v>41</v>
+      </c>
+      <c r="V16" t="n">
+        <v>37</v>
+      </c>
+      <c r="W16" t="n">
+        <v>8</v>
+      </c>
+      <c r="X16" t="n">
         <v>6</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>99</v>
@@ -2971,16 +2971,16 @@
         <v>233</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V17" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y17" t="n">
         <v>78</v>
@@ -3136,16 +3136,16 @@
         <v>111</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="n">
         <v>44</v>
@@ -3301,16 +3301,16 @@
         <v>216</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="n">
         <v>53</v>
@@ -3466,16 +3466,16 @@
         <v>163</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y20" t="n">
         <v>56</v>
@@ -3796,16 +3796,16 @@
         <v>124</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y22" t="n">
         <v>26</v>
@@ -3964,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -4126,16 +4126,16 @@
         <v>444</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="W24" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Y24" t="n">
         <v>125</v>
@@ -4291,16 +4291,16 @@
         <v>42</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V25" t="n">
+        <v>6</v>
+      </c>
+      <c r="W25" t="n">
         <v>2</v>
       </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="n">
         <v>17</v>
@@ -4456,16 +4456,16 @@
         <v>271</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V26" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y26" t="n">
         <v>71</v>
@@ -4786,16 +4786,16 @@
         <v>3508</v>
       </c>
       <c r="U28" t="n">
-        <v>12</v>
+        <v>326</v>
       </c>
       <c r="V28" t="n">
-        <v>9</v>
+        <v>384</v>
       </c>
       <c r="W28" t="n">
-        <v>9</v>
+        <v>237</v>
       </c>
       <c r="X28" t="n">
-        <v>4</v>
+        <v>155</v>
       </c>
       <c r="Y28" t="n">
         <v>991</v>
@@ -4951,16 +4951,16 @@
         <v>3927</v>
       </c>
       <c r="U29" t="n">
-        <v>10</v>
+        <v>356</v>
       </c>
       <c r="V29" t="n">
-        <v>16</v>
+        <v>436</v>
       </c>
       <c r="W29" t="n">
-        <v>18</v>
+        <v>321</v>
       </c>
       <c r="X29" t="n">
-        <v>11</v>
+        <v>204</v>
       </c>
       <c r="Y29" t="n">
         <v>1073</v>
@@ -5175,16 +5175,16 @@
         <v>201</v>
       </c>
       <c r="U31" t="n">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
       <c r="V31" t="n">
-        <v>0.25</v>
+        <v>1.667</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.583</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="Y31" t="n">
         <v>3.833</v>
@@ -5340,16 +5340,16 @@
         <v>102</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>0.393</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.214</v>
       </c>
       <c r="Y32" t="n">
         <v>0.464</v>
@@ -5505,16 +5505,16 @@
         <v>154</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>0.629</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W33" t="n">
-        <v>0.057</v>
+        <v>0.257</v>
       </c>
       <c r="X33" t="n">
-        <v>0.029</v>
+        <v>0.2</v>
       </c>
       <c r="Y33" t="n">
         <v>1.943</v>
@@ -5670,16 +5670,16 @@
         <v>395</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.118</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.471</v>
       </c>
       <c r="W34" t="n">
-        <v>0.059</v>
+        <v>1.382</v>
       </c>
       <c r="X34" t="n">
-        <v>0.029</v>
+        <v>0.912</v>
       </c>
       <c r="Y34" t="n">
         <v>3.853</v>
@@ -5835,16 +5835,16 @@
         <v>211</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.375</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="Y35" t="n">
         <v>5.188</v>
@@ -6165,16 +6165,16 @@
         <v>423</v>
       </c>
       <c r="U37" t="n">
-        <v>0.026</v>
+        <v>0.711</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>0.763</v>
       </c>
       <c r="W37" t="n">
-        <v>0.079</v>
+        <v>0.526</v>
       </c>
       <c r="X37" t="n">
-        <v>0.026</v>
+        <v>0.342</v>
       </c>
       <c r="Y37" t="n">
         <v>1.947</v>
@@ -6333,7 +6333,7 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -6495,16 +6495,16 @@
         <v>287</v>
       </c>
       <c r="U39" t="n">
+        <v>1.367</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.233</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="X39" t="n">
         <v>0.2</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>3.3</v>
@@ -6660,16 +6660,16 @@
         <v>233</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="V40" t="n">
-        <v>0.057</v>
+        <v>1.2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>0.457</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="Y40" t="n">
         <v>2.229</v>
@@ -6825,16 +6825,16 @@
         <v>111</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>0.421</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.158</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>0.421</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="Y41" t="n">
         <v>2.316</v>
@@ -6990,16 +6990,16 @@
         <v>216</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>0.846</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>0.769</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="Y42" t="n">
         <v>2.038</v>
@@ -7155,16 +7155,16 @@
         <v>163</v>
       </c>
       <c r="U43" t="n">
-        <v>0.143</v>
+        <v>0.286</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>0.643</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>0.357</v>
       </c>
       <c r="Y43" t="n">
         <v>4</v>
@@ -7485,16 +7485,16 @@
         <v>124</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>0.528</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>0.611</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>0.528</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>0.306</v>
       </c>
       <c r="Y45" t="n">
         <v>0.722</v>
@@ -7653,7 +7653,7 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="W46" t="n">
         <v>0</v>
@@ -7815,16 +7815,16 @@
         <v>444</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.056</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="W47" t="n">
-        <v>0.056</v>
+        <v>0.75</v>
       </c>
       <c r="X47" t="n">
-        <v>0.028</v>
+        <v>0.472</v>
       </c>
       <c r="Y47" t="n">
         <v>3.472</v>
@@ -7980,16 +7980,16 @@
         <v>42</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="V48" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="W48" t="n">
         <v>0.061</v>
       </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="Y48" t="n">
         <v>0.515</v>
@@ -8145,16 +8145,16 @@
         <v>271</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>0.622</v>
       </c>
       <c r="V49" t="n">
-        <v>0.054</v>
+        <v>0.432</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>0.324</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>0.216</v>
       </c>
       <c r="Y49" t="n">
         <v>1.919</v>
@@ -8475,16 +8475,16 @@
         <v>3508</v>
       </c>
       <c r="U51" t="n">
-        <v>0.316</v>
+        <v>8.579000000000001</v>
       </c>
       <c r="V51" t="n">
-        <v>0.237</v>
+        <v>10.105</v>
       </c>
       <c r="W51" t="n">
-        <v>0.237</v>
+        <v>6.237</v>
       </c>
       <c r="X51" t="n">
-        <v>0.105</v>
+        <v>4.079</v>
       </c>
       <c r="Y51" t="n">
         <v>26.079</v>
@@ -8640,16 +8640,16 @@
         <v>3927</v>
       </c>
       <c r="U52" t="n">
-        <v>0.263</v>
+        <v>9.368</v>
       </c>
       <c r="V52" t="n">
-        <v>0.421</v>
+        <v>11.474</v>
       </c>
       <c r="W52" t="n">
-        <v>0.474</v>
+        <v>8.446999999999999</v>
       </c>
       <c r="X52" t="n">
-        <v>0.289</v>
+        <v>5.368</v>
       </c>
       <c r="Y52" t="n">
         <v>28.237</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_ANADOLU EFES ISTANBUL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_ANADOLU EFES ISTANBUL.xlsx
@@ -683,13 +683,13 @@
         <v>411</v>
       </c>
       <c r="N2" t="n">
-        <v>991</v>
+        <v>457</v>
       </c>
       <c r="O2" t="n">
-        <v>1188</v>
+        <v>654</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5100901674538428</v>
+        <v>0.2808072133963074</v>
       </c>
       <c r="Q2" t="n">
         <v>236</v>
@@ -710,25 +710,25 @@
         <v>0.05710605410047231</v>
       </c>
       <c r="W2" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="X2" t="n">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.06182911120652641</v>
+        <v>0.0682696436238729</v>
       </c>
       <c r="Z2" t="n">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AA2" t="n">
-        <v>836</v>
+        <v>821</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3589523400601116</v>
+        <v>0.3525118076427651</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8341750841750841</v>
+        <v>0.6987767584097859</v>
       </c>
       <c r="AD2" t="n">
         <v>0.4199288256227758</v>
@@ -737,13 +737,13 @@
         <v>0.3007518796992481</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4375</v>
+        <v>0.4213836477987422</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3409090909090909</v>
+        <v>0.3422655298416565</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.668350168350168</v>
+        <v>1.397553516819572</v>
       </c>
       <c r="AI2" t="n">
         <v>0.6015037593984962</v>
@@ -813,13 +813,13 @@
         <v>10.81578947368421</v>
       </c>
       <c r="N3" t="n">
-        <v>26.07894736842105</v>
+        <v>12.02631578947368</v>
       </c>
       <c r="O3" t="n">
-        <v>31.26315789473684</v>
+        <v>17.21052631578947</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5100901674538428</v>
+        <v>0.2808072133963074</v>
       </c>
       <c r="Q3" t="n">
         <v>6.210526315789473</v>
@@ -840,25 +840,25 @@
         <v>0.05710605410047231</v>
       </c>
       <c r="W3" t="n">
-        <v>1.657894736842105</v>
+        <v>1.763157894736842</v>
       </c>
       <c r="X3" t="n">
-        <v>3.789473684210526</v>
+        <v>4.184210526315789</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0618291112065264</v>
+        <v>0.0682696436238729</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.5</v>
+        <v>7.394736842105263</v>
       </c>
       <c r="AA3" t="n">
-        <v>22</v>
+        <v>21.60526315789474</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3589523400601116</v>
+        <v>0.3525118076427651</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8341750841750841</v>
+        <v>0.698776758409786</v>
       </c>
       <c r="AD3" t="n">
         <v>0.4199288256227758</v>
@@ -867,19 +867,19 @@
         <v>0.3007518796992481</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4375000000000001</v>
+        <v>0.4213836477987422</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3409090909090909</v>
+        <v>0.3422655298416565</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.668350168350168</v>
+        <v>1.397553516819572</v>
       </c>
       <c r="AI3" t="n">
         <v>0.6015037593984962</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.06530612244898</v>
+        <v>1.065306122448979</v>
       </c>
       <c r="AK3" t="n">
         <v>0.690677966101695</v>
@@ -943,13 +943,13 @@
         <v>426</v>
       </c>
       <c r="N4" t="n">
-        <v>1073</v>
+        <v>438</v>
       </c>
       <c r="O4" t="n">
-        <v>1261</v>
+        <v>626</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5400428265524625</v>
+        <v>0.2680942184154176</v>
       </c>
       <c r="Q4" t="n">
         <v>268</v>
@@ -970,25 +970,25 @@
         <v>0.04582441113490364</v>
       </c>
       <c r="W4" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="X4" t="n">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0423982869379015</v>
+        <v>0.05096359743040686</v>
       </c>
       <c r="Z4" t="n">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="AA4" t="n">
-        <v>872</v>
+        <v>852</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3734475374732334</v>
+        <v>0.364882226980728</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8509119746233148</v>
+        <v>0.6996805111821086</v>
       </c>
       <c r="AD4" t="n">
         <v>0.4247226624405705</v>
@@ -997,13 +997,13 @@
         <v>0.4485981308411215</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.5050505050505051</v>
+        <v>0.4873949579831933</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3486238532110092</v>
+        <v>0.3474178403755869</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.70182394924663</v>
+        <v>1.399361022364217</v>
       </c>
       <c r="AI4" t="n">
         <v>0.897196261682243</v>
@@ -1073,13 +1073,13 @@
         <v>11.21052631578947</v>
       </c>
       <c r="N5" t="n">
-        <v>28.23684210526316</v>
+        <v>11.52631578947368</v>
       </c>
       <c r="O5" t="n">
-        <v>33.18421052631579</v>
+        <v>16.47368421052632</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5400428265524625</v>
+        <v>0.2680942184154175</v>
       </c>
       <c r="Q5" t="n">
         <v>7.052631578947368</v>
@@ -1100,25 +1100,25 @@
         <v>0.04582441113490365</v>
       </c>
       <c r="W5" t="n">
-        <v>1.315789473684211</v>
+        <v>1.526315789473684</v>
       </c>
       <c r="X5" t="n">
-        <v>2.605263157894737</v>
+        <v>3.131578947368421</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0423982869379015</v>
+        <v>0.05096359743040686</v>
       </c>
       <c r="Z5" t="n">
-        <v>8</v>
+        <v>7.789473684210527</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.94736842105263</v>
+        <v>22.42105263157895</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3734475374732334</v>
+        <v>0.3648822269807281</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8509119746233149</v>
+        <v>0.6996805111821087</v>
       </c>
       <c r="AD5" t="n">
         <v>0.4247226624405705</v>
@@ -1127,13 +1127,13 @@
         <v>0.4485981308411214</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.5050505050505051</v>
+        <v>0.4873949579831933</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3486238532110092</v>
+        <v>0.3474178403755868</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.70182394924663</v>
+        <v>1.399361022364217</v>
       </c>
       <c r="AI5" t="n">
         <v>0.8971962616822429</v>
@@ -1498,13 +1498,13 @@
         <v>16</v>
       </c>
       <c r="Y8" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.767</v>
+        <v>0.481</v>
       </c>
       <c r="AB8" t="n">
         <v>18</v>
@@ -1663,13 +1663,13 @@
         <v>6</v>
       </c>
       <c r="Y9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Z9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.867</v>
+        <v>0.8</v>
       </c>
       <c r="AB9" t="n">
         <v>20</v>
@@ -1828,13 +1828,13 @@
         <v>7</v>
       </c>
       <c r="Y10" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="Z10" t="n">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.791</v>
+        <v>0.654</v>
       </c>
       <c r="AB10" t="n">
         <v>14</v>
@@ -1855,19 +1855,19 @@
         <v>0.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="AK10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL10" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="AM10" t="n">
         <v>0.255</v>
@@ -1993,13 +1993,13 @@
         <v>31</v>
       </c>
       <c r="Y11" t="n">
-        <v>131</v>
+        <v>34</v>
       </c>
       <c r="Z11" t="n">
-        <v>149</v>
+        <v>52</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.879</v>
+        <v>0.654</v>
       </c>
       <c r="AB11" t="n">
         <v>23</v>
@@ -2023,19 +2023,19 @@
         <v>7</v>
       </c>
       <c r="AI11" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.35</v>
+        <v>0.304</v>
       </c>
       <c r="AK11" t="n">
         <v>47</v>
       </c>
       <c r="AL11" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.346</v>
+        <v>0.353</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
@@ -2158,13 +2158,13 @@
         <v>15</v>
       </c>
       <c r="Y12" t="n">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="Z12" t="n">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.856</v>
+        <v>0.674</v>
       </c>
       <c r="AB12" t="n">
         <v>15</v>
@@ -2185,22 +2185,22 @@
         <v>0.125</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="AK12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.278</v>
+        <v>0.265</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
@@ -2488,13 +2488,13 @@
         <v>13</v>
       </c>
       <c r="Y14" t="n">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="Z14" t="n">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.851</v>
+        <v>0.658</v>
       </c>
       <c r="AB14" t="n">
         <v>13</v>
@@ -2518,19 +2518,19 @@
         <v>1</v>
       </c>
       <c r="AI14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="AK14" t="n">
         <v>51</v>
       </c>
       <c r="AL14" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.375</v>
+        <v>0.378</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
@@ -2818,13 +2818,13 @@
         <v>6</v>
       </c>
       <c r="Y16" t="n">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="Z16" t="n">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.876</v>
+        <v>0.72</v>
       </c>
       <c r="AB16" t="n">
         <v>23</v>
@@ -2983,13 +2983,13 @@
         <v>10</v>
       </c>
       <c r="Y17" t="n">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="Z17" t="n">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.804</v>
+        <v>0.703</v>
       </c>
       <c r="AB17" t="n">
         <v>16</v>
@@ -3148,13 +3148,13 @@
         <v>4</v>
       </c>
       <c r="Y18" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="Z18" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.759</v>
+        <v>0.72</v>
       </c>
       <c r="AB18" t="n">
         <v>5</v>
@@ -3313,13 +3313,13 @@
         <v>4</v>
       </c>
       <c r="Y19" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="Z19" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.746</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AB19" t="n">
         <v>28</v>
@@ -3340,22 +3340,22 @@
         <v>0.375</v>
       </c>
       <c r="AH19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.571</v>
+        <v>0.591</v>
       </c>
       <c r="AK19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL19" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
@@ -3478,13 +3478,13 @@
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="Z20" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.778</v>
+        <v>0.667</v>
       </c>
       <c r="AB20" t="n">
         <v>12</v>
@@ -3808,13 +3808,13 @@
         <v>11</v>
       </c>
       <c r="Y22" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="Z22" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.929</v>
+        <v>0.8</v>
       </c>
       <c r="AB22" t="n">
         <v>4</v>
@@ -3835,22 +3835,22 @@
         <v>0.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI22" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.65</v>
+        <v>0.636</v>
       </c>
       <c r="AK22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL22" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.424</v>
+        <v>0.421</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
@@ -3973,10 +3973,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA23" t="n">
         <v>1</v>
@@ -4138,13 +4138,13 @@
         <v>17</v>
       </c>
       <c r="Y24" t="n">
-        <v>125</v>
+        <v>67</v>
       </c>
       <c r="Z24" t="n">
-        <v>156</v>
+        <v>98</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.801</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AB24" t="n">
         <v>41</v>
@@ -4168,19 +4168,19 @@
         <v>3</v>
       </c>
       <c r="AI24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AK24" t="n">
         <v>34</v>
       </c>
       <c r="AL24" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.386</v>
+        <v>0.395</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
@@ -4303,13 +4303,13 @@
         <v>2</v>
       </c>
       <c r="Y25" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="Z25" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.944</v>
+        <v>0.8</v>
       </c>
       <c r="AB25" t="n">
         <v>2</v>
@@ -4468,13 +4468,13 @@
         <v>8</v>
       </c>
       <c r="Y26" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="Z26" t="n">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.986</v>
+        <v>0.983</v>
       </c>
       <c r="AB26" t="n">
         <v>1</v>
@@ -4798,13 +4798,13 @@
         <v>155</v>
       </c>
       <c r="Y28" t="n">
-        <v>991</v>
+        <v>457</v>
       </c>
       <c r="Z28" t="n">
-        <v>1188</v>
+        <v>654</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.834</v>
+        <v>0.699</v>
       </c>
       <c r="AB28" t="n">
         <v>236</v>
@@ -4825,22 +4825,22 @@
         <v>0.301</v>
       </c>
       <c r="AH28" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="AI28" t="n">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.438</v>
+        <v>0.421</v>
       </c>
       <c r="AK28" t="n">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AL28" t="n">
-        <v>836</v>
+        <v>821</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.341</v>
+        <v>0.342</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
@@ -4963,13 +4963,13 @@
         <v>204</v>
       </c>
       <c r="Y29" t="n">
-        <v>1073</v>
+        <v>438</v>
       </c>
       <c r="Z29" t="n">
-        <v>1261</v>
+        <v>626</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.851</v>
+        <v>0.7</v>
       </c>
       <c r="AB29" t="n">
         <v>268</v>
@@ -4990,22 +4990,22 @@
         <v>0.449</v>
       </c>
       <c r="AH29" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="AI29" t="n">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.505</v>
+        <v>0.487</v>
       </c>
       <c r="AK29" t="n">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="AL29" t="n">
-        <v>872</v>
+        <v>852</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.349</v>
+        <v>0.347</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
@@ -5187,13 +5187,13 @@
         <v>1.333</v>
       </c>
       <c r="Y31" t="n">
-        <v>3.833</v>
+        <v>1.083</v>
       </c>
       <c r="Z31" t="n">
-        <v>5</v>
+        <v>2.25</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.767</v>
+        <v>0.481</v>
       </c>
       <c r="AB31" t="n">
         <v>1.5</v>
@@ -5352,13 +5352,13 @@
         <v>0.214</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.464</v>
+        <v>0.286</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.536</v>
+        <v>0.357</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.867</v>
+        <v>0.8</v>
       </c>
       <c r="AB32" t="n">
         <v>0.714</v>
@@ -5517,13 +5517,13 @@
         <v>0.2</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.943</v>
+        <v>0.971</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.457</v>
+        <v>1.486</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.791</v>
+        <v>0.654</v>
       </c>
       <c r="AB33" t="n">
         <v>0.4</v>
@@ -5544,19 +5544,19 @@
         <v>0.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.143</v>
+        <v>0.171</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.286</v>
+        <v>0.4</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.371</v>
+        <v>0.343</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.457</v>
+        <v>1.343</v>
       </c>
       <c r="AM33" t="n">
         <v>0.255</v>
@@ -5682,13 +5682,13 @@
         <v>0.912</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.853</v>
+        <v>1</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.382</v>
+        <v>1.529</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.879</v>
+        <v>0.654</v>
       </c>
       <c r="AB34" t="n">
         <v>0.676</v>
@@ -5712,19 +5712,19 @@
         <v>0.206</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.588</v>
+        <v>0.676</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.35</v>
+        <v>0.304</v>
       </c>
       <c r="AK34" t="n">
         <v>1.382</v>
       </c>
       <c r="AL34" t="n">
-        <v>4</v>
+        <v>3.912</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.346</v>
+        <v>0.353</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
@@ -5847,13 +5847,13 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="Y35" t="n">
-        <v>5.188</v>
+        <v>1.812</v>
       </c>
       <c r="Z35" t="n">
-        <v>6.062</v>
+        <v>2.688</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.856</v>
+        <v>0.674</v>
       </c>
       <c r="AB35" t="n">
         <v>0.9379999999999999</v>
@@ -5874,22 +5874,22 @@
         <v>0.125</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.125</v>
+        <v>0.188</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.438</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.286</v>
+        <v>0.333</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.625</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.25</v>
+        <v>2.125</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.278</v>
+        <v>0.265</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
@@ -6177,13 +6177,13 @@
         <v>0.342</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.947</v>
+        <v>0.658</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.289</v>
+        <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.851</v>
+        <v>0.658</v>
       </c>
       <c r="AB37" t="n">
         <v>0.342</v>
@@ -6207,19 +6207,19 @@
         <v>0.026</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.158</v>
+        <v>0.184</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="AK37" t="n">
         <v>1.342</v>
       </c>
       <c r="AL37" t="n">
-        <v>3.579</v>
+        <v>3.553</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.375</v>
+        <v>0.378</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
@@ -6507,13 +6507,13 @@
         <v>0.2</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.767</v>
+        <v>1.667</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.876</v>
+        <v>0.72</v>
       </c>
       <c r="AB39" t="n">
         <v>0.767</v>
@@ -6672,13 +6672,13 @@
         <v>0.286</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.229</v>
+        <v>1.286</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.771</v>
+        <v>1.829</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.804</v>
+        <v>0.703</v>
       </c>
       <c r="AB40" t="n">
         <v>0.457</v>
@@ -6837,13 +6837,13 @@
         <v>0.211</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.316</v>
+        <v>1.895</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.053</v>
+        <v>2.632</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.759</v>
+        <v>0.72</v>
       </c>
       <c r="AB41" t="n">
         <v>0.263</v>
@@ -7002,13 +7002,13 @@
         <v>0.154</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.038</v>
+        <v>0.885</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.731</v>
+        <v>1.577</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.746</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AB42" t="n">
         <v>1.077</v>
@@ -7029,22 +7029,22 @@
         <v>0.375</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.846</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.571</v>
+        <v>0.591</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.769</v>
+        <v>0.731</v>
       </c>
       <c r="AL42" t="n">
-        <v>2.846</v>
+        <v>2.808</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
@@ -7167,13 +7167,13 @@
         <v>0.357</v>
       </c>
       <c r="Y43" t="n">
-        <v>4</v>
+        <v>2.286</v>
       </c>
       <c r="Z43" t="n">
-        <v>5.143</v>
+        <v>3.429</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.778</v>
+        <v>0.667</v>
       </c>
       <c r="AB43" t="n">
         <v>0.857</v>
@@ -7497,13 +7497,13 @@
         <v>0.306</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.722</v>
+        <v>0.222</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.778</v>
+        <v>0.278</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.929</v>
+        <v>0.8</v>
       </c>
       <c r="AB45" t="n">
         <v>0.111</v>
@@ -7524,22 +7524,22 @@
         <v>0.5</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.361</v>
+        <v>0.389</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.556</v>
+        <v>0.611</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.65</v>
+        <v>0.636</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.694</v>
+        <v>0.667</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.639</v>
+        <v>1.583</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.424</v>
+        <v>0.421</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
@@ -7662,10 +7662,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="AA46" t="n">
         <v>1</v>
@@ -7827,13 +7827,13 @@
         <v>0.472</v>
       </c>
       <c r="Y47" t="n">
-        <v>3.472</v>
+        <v>1.861</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.333</v>
+        <v>2.722</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.801</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="AB47" t="n">
         <v>1.139</v>
@@ -7857,19 +7857,19 @@
         <v>0.083</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.083</v>
+        <v>0.139</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AK47" t="n">
         <v>0.944</v>
       </c>
       <c r="AL47" t="n">
-        <v>2.444</v>
+        <v>2.389</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.386</v>
+        <v>0.395</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
@@ -7992,13 +7992,13 @@
         <v>0.061</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.515</v>
+        <v>0.121</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.545</v>
+        <v>0.152</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.944</v>
+        <v>0.8</v>
       </c>
       <c r="AB48" t="n">
         <v>0.061</v>
@@ -8157,13 +8157,13 @@
         <v>0.216</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.919</v>
+        <v>1.541</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.946</v>
+        <v>1.568</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.986</v>
+        <v>0.983</v>
       </c>
       <c r="AB49" t="n">
         <v>0.027</v>
@@ -8487,13 +8487,13 @@
         <v>4.079</v>
       </c>
       <c r="Y51" t="n">
-        <v>26.079</v>
+        <v>12.026</v>
       </c>
       <c r="Z51" t="n">
-        <v>31.263</v>
+        <v>17.211</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.834</v>
+        <v>0.699</v>
       </c>
       <c r="AB51" t="n">
         <v>6.211</v>
@@ -8514,22 +8514,22 @@
         <v>0.301</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.658</v>
+        <v>1.763</v>
       </c>
       <c r="AI51" t="n">
-        <v>3.789</v>
+        <v>4.184</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.438</v>
+        <v>0.421</v>
       </c>
       <c r="AK51" t="n">
-        <v>7.5</v>
+        <v>7.395</v>
       </c>
       <c r="AL51" t="n">
-        <v>22</v>
+        <v>21.605</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.341</v>
+        <v>0.342</v>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
@@ -8652,13 +8652,13 @@
         <v>5.368</v>
       </c>
       <c r="Y52" t="n">
-        <v>28.237</v>
+        <v>11.526</v>
       </c>
       <c r="Z52" t="n">
-        <v>33.184</v>
+        <v>16.474</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.851</v>
+        <v>0.7</v>
       </c>
       <c r="AB52" t="n">
         <v>7.053</v>
@@ -8679,22 +8679,22 @@
         <v>0.449</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.316</v>
+        <v>1.526</v>
       </c>
       <c r="AI52" t="n">
-        <v>2.605</v>
+        <v>3.132</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.505</v>
+        <v>0.487</v>
       </c>
       <c r="AK52" t="n">
-        <v>8</v>
+        <v>7.789</v>
       </c>
       <c r="AL52" t="n">
-        <v>22.947</v>
+        <v>22.421</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.349</v>
+        <v>0.347</v>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
